--- a/util/report_chennai.xlsx
+++ b/util/report_chennai.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G531"/>
+  <dimension ref="A1:G626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52.2" customWidth="1" min="2" max="2"/>
@@ -19013,6 +19013,3331 @@
         </is>
       </c>
     </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>BAPHY105</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Engineering Physics</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>3</v>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>B2+TB2</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>BAEEE101</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Basic Engineering</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>3</v>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>BAFLC100</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Foreign Language</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>1</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>TE2</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>BACSE205</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Fundamentals of Artificial Intelligence and Machine Learning</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>3</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>A1+TA1</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>MAHESWARI S</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>BACSE205</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Fundamentals of Artificial Intelligence and Machine Learning</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>1</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>L11+L12</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>MAHESWARI S</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>BACSE205</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Fundamentals of Artificial Intelligence and Machine Learning</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>3</v>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>A1+TA1</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>BACSE205</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Fundamentals of Artificial Intelligence and Machine Learning</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>1</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>L37+L38</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>BACSE205</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Fundamentals of Artificial Intelligence and Machine Learning</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>3</v>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>A1+TA1</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>V. BRINDHA</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>BACSE205</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Fundamentals of Artificial Intelligence and Machine Learning</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>1</v>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>L37+L38</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>V. BRINDHA</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>BACSE205</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Fundamentals of Artificial Intelligence and Machine Learning</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>3</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>A2+TA2</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>MAHESWARI S</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>BACSE205</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Fundamentals of Artificial Intelligence and Machine Learning</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>1</v>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>L7+L8</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>MAHESWARI S</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>3</v>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>C1+TC1</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>A. K ILAVARASI</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>1</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>L31+L32</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>A. K ILAVARASI</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>3</v>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>C1+TC1</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>ALOK CHAUHAN</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>1</v>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>L31+L32</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>ALOK CHAUHAN</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>3</v>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>C1+TC1</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>RISHIKESHAN C A</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>1</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>L33+L34</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>RISHIKESHAN C A</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>3</v>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>C1+TC1</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>SUGUNA</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>1</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>L33+L34</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>SUGUNA</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>3</v>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>C1+TC1</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>D KAVITHA</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>1</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>L33+L34</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>D KAVITHA</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>3</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>C1+TC1</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>BRINDHA S</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>1</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>L31+L32</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>BRINDHA S</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>3</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>C1+TC1</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>REENA ROY R</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>1</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>L31+L32</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>REENA ROY R</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>3</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>C1+TC1</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>PRAVEEN JOE I R</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>1</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>L33+L34</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>PRAVEEN JOE I R</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>3</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>C1+TC1</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>GANESH N</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>1</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>L33+L34</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>GANESH N</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>3</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>C1+TC1</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>SUGANYA R</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>1</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>L33+L34</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>SUGANYA R</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>3</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>C2+TC2</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>A. K ILAVARASI</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>1</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>L1+L2</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>A. K ILAVARASI</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>3</v>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>C2+TC2</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>ALOK CHAUHAN</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>1</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>L1+L2</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>ALOK CHAUHAN</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>3</v>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>C2+TC2</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>RISHIKESHAN C A</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>1</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>L3+L4</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>RISHIKESHAN C A</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>3</v>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>C2+TC2</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>SUGUNA</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>1</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>L3+L4</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>SUGUNA</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>3</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>C2+TC2</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>D KAVITHA</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>1</v>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>L3+L4</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>D KAVITHA</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>3</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>C2+TC2</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>BRINDHA S</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>1</v>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>L1+L2</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>BRINDHA S</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>3</v>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>C2+TC2</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN M</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>1</v>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>L1+L2</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN M</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>3</v>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>C2+TC2</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>REENA ROY R</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>1</v>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>L1+L2</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>REENA ROY R</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>3</v>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>C2+TC2</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>PRAVEEN JOE I R</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>1</v>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>L3+L4</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>PRAVEEN JOE I R</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>3</v>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>C2+TC2</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>SUGANYA R</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>BACSE204</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>1</v>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>L3+L4</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>SUGANYA R</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>3</v>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>PRADEEP K V</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>1</v>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>L23+L24</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>PRADEEP K V</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>3</v>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>ANANDAN P</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>1</v>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>L49+L50</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>ANANDAN P</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>3</v>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>RAVICHANDRAN M</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>1</v>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>L51+L52</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>RAVICHANDRAN M</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>3</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>SUDHA A</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>1</v>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>L23+L24</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>SUDHA A</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>3</v>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>A SWAMINATHAN</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>1</v>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>L23+L24</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>A SWAMINATHAN</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>3</v>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>RADHA R</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>1</v>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>L23+L24</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>RADHA R</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>3</v>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>NOEL JEYGAR ROBERT V</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>1</v>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>L23+L24</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>NOEL JEYGAR ROBERT V</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>3</v>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>DEEPA NIVETHIKA S</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>1</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>L49+L50</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>DEEPA NIVETHIKA S</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>3</v>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>SANGEETHA N</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>1</v>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>L49+L50</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>SANGEETHA N</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>3</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>MAHESWARI P</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>1</v>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>L51+L52</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>MAHESWARI P</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>3</v>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>PRIYANKA MISHRA</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>1</v>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>L19+L20</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>PRIYANKA MISHRA</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>3</v>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>ANANDAN P</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>1</v>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>L19+L20</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>ANANDAN P</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>3</v>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>A.PRAVIN RENOLD</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>1</v>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>L21+L22</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>A.PRAVIN RENOLD</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>3</v>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>RAVICHANDRAN M</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>1</v>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>L21+L22</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>RAVICHANDRAN M</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>3</v>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>SIVAKUMAR P</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>1</v>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>L19+L20</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>SIVAKUMAR P</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>3</v>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>A SWAMINATHAN</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>1</v>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>L19+L20</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>A SWAMINATHAN</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>3</v>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>RADHA R</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>1</v>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>L19+L20</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>RADHA R</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>3</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>NOEL JEYGAR ROBERT V</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>1</v>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>L19+L20</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>NOEL JEYGAR ROBERT V</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>3</v>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>AMRIT PAL</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>1</v>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>L19+L20</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>AMRIT PAL</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>3</v>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>SANGEETHA N</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>BACSE203</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>1</v>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>L19+L20</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>SANGEETHA N</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>BACSE312</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Embedded Systems</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>3</v>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>B1+TB1</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>BACSE312</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Embedded Systems</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>1</v>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>L29+L30</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>BAHUM103</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Ethics and Values</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>2</v>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>BAMGT101</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Open elective (Ancillary)</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>3</v>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>D1+TD1</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/util/report_chennai.xlsx
+++ b/util/report_chennai.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G626"/>
+  <dimension ref="A1:G717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52.2" customWidth="1" min="2" max="2"/>
@@ -22338,6 +22338,3191 @@
         </is>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>BACHY105</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Applied Chemistry</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>3</v>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>E1+TE1</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>BACHY105</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Applied Chemistry</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>1</v>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>BAMAT207</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Probability and Statistics</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>3</v>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>B1+TB1</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>BAHSM100</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>HSM COURSES/open elective</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>3</v>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>G1+TG1</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>BAHSM100</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>HSM COURSES/open elective</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>3</v>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>G2+TG2</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>3</v>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>AB1-301</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>1</v>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>L5+L6</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>3</v>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>AB1-302</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>1</v>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>L49+L50</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>3</v>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>AB1-401</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>1</v>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>L39+L40</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>3</v>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>AB1-402</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>1</v>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>L49+L50</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>3</v>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>AB1-408</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>1</v>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>L51+L52</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>3</v>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>AB1-409</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>1</v>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>L23+L24</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>3</v>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>AB1-410</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>1</v>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>L55+L56</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>3</v>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>AB1-411</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>1</v>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>L39+L40</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>3</v>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>AB1-501</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>1</v>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>L39+L40</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>3</v>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>AB1-502</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>1</v>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>L51+L52</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>3</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>AB1-508</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>1</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>L5+L6</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>3</v>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>F1+TF1</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>AB1-509</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>1</v>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>L23+L24</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>3</v>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>AB1-301</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>1</v>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>L3+L4</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>3</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>AB1-302</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>1</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>L19+L20</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>3</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>AB1-401</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>1</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>L9+L10</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>3</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>AB1-402</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>1</v>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>L19+L20</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>3</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>AB1-408</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>1</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>L21+L22</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>3</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>AB1-409</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>1</v>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>L53+L54</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>3</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>AB1-410</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>1</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>L7+L8</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>3</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>AB1-411</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>1</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>L9+L10</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>3</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>AB1-501</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>1</v>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>L41+L42</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>3</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>AB1-502</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>1</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>L21+L22</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>AB1-213</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>3</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>AB1-508</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>1</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>L7+L8</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>3</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>F2+TF2</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>AB1-509</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>BACSE103</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Computation Structures</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>1</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>L53+L54</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>AB1-506A</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>2</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>AB1-301</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>2</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>L5+L6+L43+L44</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>2</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>AB1-302</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>2</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>L11+L12+L49+L50</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>2</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>AB1-401</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>2</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>L11+L12+L51+L52</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>2</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>AB1-402</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>2</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>L23+L24+L37+L38</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>2</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>AB1-408</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>2</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>L29+L30+L31+L32</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>2</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>AB1-409</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>2</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>L39+L40+L51+L52</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>2</v>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>AB1-410</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>2</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>L33+L34+L55+L56</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>2</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>AB1-411</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>2</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>AB1-501</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>2</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>L29+L30+L39+L40</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>2</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>AB1-502</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>2</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>2</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>AB1-508</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>2</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>AB1-509</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>2</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>AB1-301</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>2</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>L1+L2+L15+L16</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>2</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>AB1-302</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D704" t="n">
+        <v>2</v>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>L3+L4+L19+L20</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>2</v>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>AB1-401</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>2</v>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>L7+L8+L21+L22</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>2</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>AB1-402</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D708" t="n">
+        <v>2</v>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>AB1-408</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D709" t="n">
+        <v>2</v>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>AB1-409</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D710" t="n">
+        <v>2</v>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>AB1-410</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>2</v>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>AB1-411</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D712" t="n">
+        <v>2</v>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>AB1-501</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>2</v>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>L13+L14+L27+L28</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D714" t="n">
+        <v>2</v>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>AB1-502</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>2</v>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>AB1-508</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>ELA</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>2</v>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>L9+L10+L21+L22</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>BACSE104</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Structured and Object-Oriented Programming</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D717" t="n">
+        <v>2</v>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>AB1-509</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
